--- a/SGC-CKN/Excel/8efd43ff-c742-444a-8336-8ac3312f421c_Thanh_Hoá_P7-21_D800_01-01-2026.xlsx
+++ b/SGC-CKN/Excel/8efd43ff-c742-444a-8336-8ac3312f421c_Thanh_Hoá_P7-21_D800_01-01-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>11:50 01/01/2026</t>
+    <t>11:30 01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>21:20 01/01/2026</t>
+    <t>21:20 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">11:50
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:54
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>Chiều dài tính toán (7.12 - 3.36)</t>
@@ -116,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">11:55
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:03
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>Chiều dài tính toán (19.12 - 7.12)</t>
@@ -133,11 +133,11 @@
   </si>
   <si>
     <t xml:space="preserve">12:04
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:06
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>Số liệu 17.32 ghi sau 19.12 trong biên bản gây mâu thuẫn về độ sâu tăng dần</t>
@@ -150,11 +150,11 @@
   </si>
   <si>
     <t xml:space="preserve">14:07
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:54
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t/>
@@ -167,11 +167,11 @@
   </si>
   <si>
     <t xml:space="preserve">14:55
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:49
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -181,11 +181,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:50
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:36
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -195,11 +195,11 @@
   </si>
   <si>
     <t xml:space="preserve">17:37
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:59
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -209,11 +209,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:00
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:27
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -223,11 +223,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:31
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:00
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -237,7 +237,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:20
-01/01/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc tại 44.75m</t>

--- a/SGC-CKN/Excel/8efd43ff-c742-444a-8336-8ac3312f421c_Thanh_Hoá_P7-21_D800_01-01-2026.xlsx
+++ b/SGC-CKN/Excel/8efd43ff-c742-444a-8336-8ac3312f421c_Thanh_Hoá_P7-21_D800_01-01-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">11:50
+    <t xml:space="preserve">11:30
 01/04/2026</t>
   </si>
   <si>
@@ -212,18 +212,14 @@
 01/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:27
-01/04/2026</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">18:31
 01/04/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:00
@@ -277,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -319,12 +315,6 @@
     </font>
     <font>
       <color rgb="FF065F46"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -376,7 +366,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -431,11 +421,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -556,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -600,29 +585,35 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -660,22 +651,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1261,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.36</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.12</v>
       </c>
       <c r="H11" s="5">
-        <v>0.07</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="5">
-        <v>3.76</v>
+        <v>7.12</v>
       </c>
       <c r="J11" s="8">
-        <v>56.4</v>
+        <v>17.8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1299,16 +1281,16 @@
         <v>-7.12</v>
       </c>
       <c r="G12" s="9">
-        <v>-19.12</v>
+        <v>-9.12</v>
       </c>
       <c r="H12" s="9">
         <v>0.13</v>
       </c>
       <c r="I12" s="9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>35</v>
@@ -1331,7 +1313,7 @@
         <v>39</v>
       </c>
       <c r="F13" s="12">
-        <v>-19.12</v>
+        <v>-9.12</v>
       </c>
       <c r="G13" s="12">
         <v>-17.32</v>
@@ -1340,10 +1322,10 @@
         <v>2.03</v>
       </c>
       <c r="I13" s="12">
-        <v>1.8</v>
+        <v>8.2</v>
       </c>
       <c r="J13" s="15">
-        <v>0.89</v>
+        <v>4.03</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>40</v>
@@ -1404,210 +1386,210 @@
         <v>-21.62</v>
       </c>
       <c r="G15" s="19">
-        <v>-26.12</v>
+        <v>-26.62</v>
       </c>
       <c r="H15" s="19">
         <v>0.9</v>
       </c>
       <c r="I15" s="19">
-        <v>4.5</v>
-      </c>
-      <c r="J15" s="22">
         <v>5</v>
+      </c>
+      <c r="J15" s="8">
+        <v>5.56</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="23">
-        <v>-26.12</v>
-      </c>
-      <c r="G16" s="23">
+      <c r="F16" s="22">
+        <v>-26.62</v>
+      </c>
+      <c r="G16" s="22">
         <v>-36.2</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>1.77</v>
       </c>
-      <c r="I16" s="23">
-        <v>10.08</v>
+      <c r="I16" s="22">
+        <v>9.58</v>
       </c>
       <c r="J16" s="8">
-        <v>5.71</v>
-      </c>
-      <c r="K16" s="24" t="s">
+        <v>5.42</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-36.2</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-38.2</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>0.37</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>2</v>
       </c>
       <c r="J17" s="8">
         <v>5.45</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-38.2</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-39.5</v>
       </c>
-      <c r="H18" s="29">
-        <v>0.45</v>
-      </c>
-      <c r="I18" s="29">
+      <c r="H18" s="28">
+        <v>0.52</v>
+      </c>
+      <c r="I18" s="28">
         <v>1.3</v>
       </c>
-      <c r="J18" s="22">
-        <v>2.89</v>
-      </c>
-      <c r="K18" s="30" t="s">
+      <c r="J18" s="15">
+        <v>2.52</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="F19" s="31">
+        <v>-39.5</v>
+      </c>
+      <c r="G19" s="31">
+        <v>-43.1</v>
+      </c>
+      <c r="H19" s="31">
+        <v>1.48</v>
+      </c>
+      <c r="I19" s="31">
+        <v>3.6</v>
+      </c>
+      <c r="J19" s="15">
+        <v>2.43</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="32">
-        <v>-39.5</v>
-      </c>
-      <c r="G19" s="32">
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="34">
         <v>-43.1</v>
       </c>
-      <c r="H19" s="32">
-        <v>1.48</v>
-      </c>
-      <c r="I19" s="32">
-        <v>3.6</v>
-      </c>
-      <c r="J19" s="22">
-        <v>2.43</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="37" t="s">
+      <c r="G20" s="34">
+        <v>-44.75</v>
+      </c>
+      <c r="H20" s="34">
+        <v>1.33</v>
+      </c>
+      <c r="I20" s="34">
+        <v>1.65</v>
+      </c>
+      <c r="J20" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="K20" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="35">
-        <v>-43.1</v>
-      </c>
-      <c r="G20" s="35">
-        <v>-44.75</v>
-      </c>
-      <c r="H20" s="35">
-        <v>1.33</v>
-      </c>
-      <c r="I20" s="35">
-        <v>1.65</v>
-      </c>
-      <c r="J20" s="22">
-        <v>1.24</v>
-      </c>
-      <c r="K20" s="36" t="s">
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1702,31 +1684,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,19 +1725,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.36</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.12</v>
       </c>
       <c r="G2" s="5">
-        <v>0.07</v>
+        <v>0.4</v>
       </c>
       <c r="H2" s="5">
-        <v>3.76</v>
+        <v>7.12</v>
       </c>
       <c r="I2" s="8">
-        <v>56.4</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1775,16 +1757,16 @@
         <v>-7.12</v>
       </c>
       <c r="F3" s="9">
-        <v>-19.12</v>
+        <v>-9.12</v>
       </c>
       <c r="G3" s="9">
         <v>0.13</v>
       </c>
       <c r="H3" s="9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I3" s="8">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1801,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-19.12</v>
+        <v>-9.12</v>
       </c>
       <c r="F4" s="12">
         <v>-17.32</v>
@@ -1810,10 +1792,10 @@
         <v>2.03</v>
       </c>
       <c r="H4" s="12">
-        <v>1.8</v>
+        <v>8.2</v>
       </c>
       <c r="I4" s="15">
-        <v>0.89</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1862,70 +1844,70 @@
         <v>-21.62</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.12</v>
+        <v>-26.62</v>
       </c>
       <c r="G6" s="19">
         <v>0.9</v>
       </c>
       <c r="H6" s="19">
-        <v>4.5</v>
-      </c>
-      <c r="I6" s="22">
         <v>5</v>
       </c>
+      <c r="I6" s="8">
+        <v>5.56</v>
+      </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
-        <v>-26.12</v>
-      </c>
-      <c r="F7" s="23">
+      <c r="E7" s="22">
+        <v>-26.62</v>
+      </c>
+      <c r="F7" s="22">
         <v>-36.2</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1.77</v>
       </c>
-      <c r="H7" s="23">
-        <v>10.08</v>
+      <c r="H7" s="22">
+        <v>9.58</v>
       </c>
       <c r="I7" s="8">
-        <v>5.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-36.2</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-38.2</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>0.37</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>2</v>
       </c>
       <c r="I8" s="8">
@@ -1933,119 +1915,119 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-38.2</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-39.5</v>
       </c>
-      <c r="G9" s="29">
-        <v>0.45</v>
-      </c>
-      <c r="H9" s="29">
+      <c r="G9" s="28">
+        <v>0.52</v>
+      </c>
+      <c r="H9" s="28">
         <v>1.3</v>
       </c>
-      <c r="I9" s="22">
-        <v>2.89</v>
+      <c r="I9" s="15">
+        <v>2.52</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>-39.5</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-43.1</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <v>1.48</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>3.6</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="15">
         <v>2.43</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="C11" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-43.1</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-44.75</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>1.33</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>1.65</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="15">
         <v>1.24</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-3.36</v>
-      </c>
-      <c r="F12" s="40">
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
         <v>-44.75</v>
       </c>
-      <c r="G12" s="40">
-        <v>9.32</v>
-      </c>
-      <c r="H12" s="40">
-        <v>44.99</v>
-      </c>
-      <c r="I12" s="40">
-        <v>4.83</v>
+      <c r="G12" s="39">
+        <v>9.72</v>
+      </c>
+      <c r="H12" s="39">
+        <v>44.75</v>
+      </c>
+      <c r="I12" s="39">
+        <v>4.61</v>
       </c>
     </row>
   </sheetData>
